--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A11BE3-BBE8-AA43-8360-661DE8D1C746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C96B62D-C516-454B-BA22-6A3F857D525C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="5480" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="2200" yWindow="3820" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="2" r:id="rId1"/>
@@ -1787,6 +1787,21 @@
       <c r="C37">
         <v>10</v>
       </c>
+      <c r="E37">
+        <v>9</v>
+      </c>
+      <c r="H37">
+        <v>10</v>
+      </c>
+      <c r="I37">
+        <v>10</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+      <c r="K37">
+        <v>10</v>
+      </c>
     </row>
     <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B38">
@@ -1795,6 +1810,21 @@
       <c r="C38">
         <v>12</v>
       </c>
+      <c r="E38">
+        <v>12</v>
+      </c>
+      <c r="H38">
+        <v>12</v>
+      </c>
+      <c r="I38">
+        <v>12</v>
+      </c>
+      <c r="J38">
+        <v>11</v>
+      </c>
+      <c r="K38">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B39">
@@ -1803,6 +1833,21 @@
       <c r="C39">
         <v>8</v>
       </c>
+      <c r="E39">
+        <v>6</v>
+      </c>
+      <c r="H39">
+        <v>6</v>
+      </c>
+      <c r="I39">
+        <v>8</v>
+      </c>
+      <c r="J39">
+        <v>4</v>
+      </c>
+      <c r="K39">
+        <v>4</v>
+      </c>
     </row>
     <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B40">
@@ -1811,6 +1856,18 @@
       <c r="C40">
         <v>18</v>
       </c>
+      <c r="E40">
+        <v>18</v>
+      </c>
+      <c r="I40">
+        <v>18</v>
+      </c>
+      <c r="J40">
+        <v>12</v>
+      </c>
+      <c r="K40">
+        <v>18</v>
+      </c>
     </row>
     <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B41">
@@ -1819,6 +1876,18 @@
       <c r="C41">
         <v>10</v>
       </c>
+      <c r="E41">
+        <v>8</v>
+      </c>
+      <c r="I41">
+        <v>10</v>
+      </c>
+      <c r="J41">
+        <v>7</v>
+      </c>
+      <c r="K41">
+        <v>7</v>
+      </c>
     </row>
     <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B42">
@@ -1827,6 +1896,18 @@
       <c r="C42">
         <v>18</v>
       </c>
+      <c r="E42">
+        <v>14</v>
+      </c>
+      <c r="I42">
+        <v>18</v>
+      </c>
+      <c r="J42">
+        <v>16</v>
+      </c>
+      <c r="K42">
+        <v>17</v>
+      </c>
     </row>
     <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B43">
@@ -1835,12 +1916,36 @@
       <c r="C43">
         <v>9</v>
       </c>
+      <c r="E43">
+        <v>9</v>
+      </c>
+      <c r="I43">
+        <v>9</v>
+      </c>
+      <c r="J43">
+        <v>9</v>
+      </c>
+      <c r="K43">
+        <v>9</v>
+      </c>
     </row>
     <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B44">
         <v>8</v>
       </c>
       <c r="C44">
+        <v>5</v>
+      </c>
+      <c r="E44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>5</v>
+      </c>
+      <c r="J44">
+        <v>5</v>
+      </c>
+      <c r="K44">
         <v>5</v>
       </c>
     </row>
@@ -1851,6 +1956,18 @@
       <c r="C45">
         <v>10</v>
       </c>
+      <c r="E45">
+        <v>7</v>
+      </c>
+      <c r="I45">
+        <v>10</v>
+      </c>
+      <c r="J45">
+        <v>8</v>
+      </c>
+      <c r="K45">
+        <v>10</v>
+      </c>
     </row>
     <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B46">
@@ -1871,7 +1988,7 @@
       </c>
       <c r="E47">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="F47">
         <f t="shared" si="9"/>
@@ -1883,19 +2000,19 @@
       </c>
       <c r="H47">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I47">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J47">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="K47">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L47">
         <f t="shared" si="9"/>

--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E61EB2-B5BD-924A-8BB6-315459BFE20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A837104-E7D2-BC40-9FCD-CA7BFFB30695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21680" yWindow="4720" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="24120" yWindow="5440" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="2" r:id="rId1"/>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="K6">
         <f>(D6+E6+D$30+D$31)*D$3</f>
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="L6">
         <f>(F6+F$30+F$31)*F$3</f>
@@ -1136,11 +1136,11 @@
       </c>
       <c r="P6" s="3">
         <f>SUM(K6:O6)</f>
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="Q6" s="3">
         <f>100*P6/(100*SUM($D$4:$I$4))</f>
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="K7">
         <f>(D7+E7+D$30+D$31)*D$3</f>
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="L7">
         <f t="shared" ref="L7:L12" si="3">(F7+F$30+F$31)*F$3</f>
@@ -1181,11 +1181,11 @@
       </c>
       <c r="P7" s="3">
         <f t="shared" ref="P7:P12" si="4">SUM(K7:O7)</f>
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" ref="Q7:Q15" si="5">100*P7/(100*SUM($D$4:$I$4))</f>
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="K8">
         <f t="shared" ref="K8:K26" si="6">(D8+E8+D$30+D$31)*D$3</f>
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="L8">
         <f t="shared" si="3"/>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="P8" s="3">
         <f t="shared" ref="P8" si="7">SUM(K8:O8)</f>
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="5"/>
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="K9">
         <f t="shared" si="6"/>
-        <v>14.8</v>
+        <v>14.600000000000001</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
@@ -1271,11 +1271,11 @@
       </c>
       <c r="P9" s="3">
         <f t="shared" si="4"/>
-        <v>14.8</v>
+        <v>14.600000000000001</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="5"/>
-        <v>74</v>
+        <v>73.000000000000014</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="K10">
         <f t="shared" si="6"/>
-        <v>17.600000000000001</v>
+        <v>17.400000000000002</v>
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
@@ -1316,11 +1316,11 @@
       </c>
       <c r="P10" s="3">
         <f t="shared" si="4"/>
-        <v>17.600000000000001</v>
+        <v>17.400000000000002</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" si="5"/>
-        <v>88.000000000000014</v>
+        <v>87.000000000000014</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="6"/>
-        <v>21.400000000000002</v>
+        <v>21.200000000000003</v>
       </c>
       <c r="L11">
         <f t="shared" si="3"/>
@@ -1361,11 +1361,11 @@
       </c>
       <c r="P11" s="3">
         <f t="shared" si="4"/>
-        <v>21.400000000000002</v>
+        <v>21.200000000000003</v>
       </c>
       <c r="Q11" s="3">
         <f t="shared" si="5"/>
-        <v>107</v>
+        <v>106.00000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="K12">
         <f t="shared" si="6"/>
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="L12">
         <f t="shared" si="3"/>
@@ -1406,11 +1406,11 @@
       </c>
       <c r="P12" s="3">
         <f t="shared" si="4"/>
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="Q12" s="3">
         <f t="shared" si="5"/>
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -1431,12 +1431,31 @@
       </c>
       <c r="K13">
         <f t="shared" si="6"/>
-        <v>19.8</v>
-      </c>
-      <c r="P13" s="3"/>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="L13">
+        <f t="shared" ref="L13:L15" si="8">(F13+F$30+F$31)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f t="shared" ref="M13:M15" si="9">(G13+G$30)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <f t="shared" ref="N13:N15" si="10">(H13+H$30+$H$31)*H$3</f>
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <f t="shared" ref="O13:O15" si="11">(I13+I$30)*I$3</f>
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" ref="P13:P15" si="12">SUM(K13:O13)</f>
+        <v>19.600000000000001</v>
+      </c>
       <c r="Q13" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98.000000000000014</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
@@ -1457,12 +1476,31 @@
       </c>
       <c r="K14">
         <f t="shared" si="6"/>
-        <v>19.200000000000003</v>
-      </c>
-      <c r="P14" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
       <c r="Q14" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
@@ -1483,12 +1521,31 @@
       </c>
       <c r="K15">
         <f t="shared" si="6"/>
-        <v>18.600000000000001</v>
-      </c>
-      <c r="P15" s="3"/>
+        <v>18.400000000000002</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <f t="shared" si="12"/>
+        <v>18.400000000000002</v>
+      </c>
       <c r="Q15" s="3">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>92.000000000000014</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -1512,15 +1569,40 @@
       <c r="C18" t="s">
         <v>24</v>
       </c>
+      <c r="D18">
+        <v>94</v>
+      </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="K18">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <f t="shared" ref="L18" si="13">(F18+F$30+F$31)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <f t="shared" ref="M18" si="14">(G18+G$30)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <f t="shared" ref="N18" si="15">(H18+H$30+$H$31)*H$3</f>
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <f t="shared" ref="O18" si="16">(I18+I$30)*I$3</f>
+        <v>0</v>
+      </c>
+      <c r="P18" s="3">
+        <f t="shared" ref="P18" si="17">SUM(K18:O18)</f>
+        <v>20</v>
+      </c>
+      <c r="Q18" s="3">
+        <f t="shared" ref="Q18" si="18">100*P18/(100*SUM($D$4:$I$4))</f>
+        <v>100</v>
+      </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19">
@@ -1532,15 +1614,40 @@
       <c r="C19" t="s">
         <v>33</v>
       </c>
+      <c r="D19">
+        <v>99</v>
+      </c>
       <c r="E19">
         <v>3</v>
       </c>
       <c r="K19">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="L19">
+        <f t="shared" ref="L19:L26" si="19">(F19+F$30+F$31)*F$3</f>
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <f t="shared" ref="M19:M26" si="20">(G19+G$30)*G$3</f>
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <f t="shared" ref="N19:N26" si="21">(H19+H$30+$H$31)*H$3</f>
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <f t="shared" ref="O19:O26" si="22">(I19+I$30)*I$3</f>
+        <v>0</v>
+      </c>
+      <c r="P19" s="3">
+        <f t="shared" ref="P19:P26" si="23">SUM(K19:O19)</f>
+        <v>21</v>
+      </c>
+      <c r="Q19" s="3">
+        <f t="shared" ref="Q19:Q26" si="24">100*P19/(100*SUM($D$4:$I$4))</f>
+        <v>105</v>
+      </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20">
@@ -1552,15 +1659,40 @@
       <c r="C20" t="s">
         <v>39</v>
       </c>
+      <c r="D20">
+        <v>76</v>
+      </c>
       <c r="E20">
         <v>3</v>
       </c>
       <c r="K20">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="2"/>
+        <v>16.400000000000002</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <f t="shared" si="23"/>
+        <v>16.400000000000002</v>
+      </c>
+      <c r="Q20" s="3">
+        <f t="shared" si="24"/>
+        <v>82.000000000000014</v>
+      </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21">
@@ -1572,15 +1704,40 @@
       <c r="C21" t="s">
         <v>48</v>
       </c>
+      <c r="D21">
+        <v>91</v>
+      </c>
       <c r="E21">
         <v>3</v>
       </c>
       <c r="K21">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="2"/>
+        <v>19.400000000000002</v>
+      </c>
+      <c r="L21">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P21" s="3">
+        <f t="shared" si="23"/>
+        <v>19.400000000000002</v>
+      </c>
+      <c r="Q21" s="3">
+        <f t="shared" si="24"/>
+        <v>97.000000000000014</v>
+      </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22">
@@ -1592,12 +1749,40 @@
       <c r="C22" t="s">
         <v>51</v>
       </c>
+      <c r="D22">
+        <v>96</v>
+      </c>
+      <c r="E22">
+        <v>3</v>
+      </c>
       <c r="K22">
         <f t="shared" si="6"/>
-        <v>0.8</v>
-      </c>
-      <c r="P22" s="3"/>
-      <c r="Q22" s="2"/>
+        <v>20.400000000000002</v>
+      </c>
+      <c r="L22">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <f t="shared" si="23"/>
+        <v>20.400000000000002</v>
+      </c>
+      <c r="Q22" s="3">
+        <f t="shared" si="24"/>
+        <v>102.00000000000001</v>
+      </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23">
@@ -1609,15 +1794,40 @@
       <c r="C23" t="s">
         <v>57</v>
       </c>
+      <c r="D23">
+        <v>96</v>
+      </c>
       <c r="E23">
         <v>3</v>
       </c>
       <c r="K23">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="2"/>
+        <v>20.400000000000002</v>
+      </c>
+      <c r="L23">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P23" s="3">
+        <f t="shared" si="23"/>
+        <v>20.400000000000002</v>
+      </c>
+      <c r="Q23" s="3">
+        <f t="shared" si="24"/>
+        <v>102.00000000000001</v>
+      </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24">
@@ -1629,15 +1839,40 @@
       <c r="C24" t="s">
         <v>60</v>
       </c>
+      <c r="D24">
+        <v>99</v>
+      </c>
       <c r="E24">
         <v>3</v>
       </c>
       <c r="K24">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="L24">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <f t="shared" si="23"/>
+        <v>21</v>
+      </c>
+      <c r="Q24" s="3">
+        <f t="shared" si="24"/>
+        <v>105</v>
+      </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25">
@@ -1649,15 +1884,40 @@
       <c r="C25" t="s">
         <v>63</v>
       </c>
+      <c r="D25">
+        <v>93</v>
+      </c>
       <c r="E25">
         <v>3</v>
       </c>
       <c r="K25">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="2"/>
+        <v>19.8</v>
+      </c>
+      <c r="L25">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <f t="shared" si="23"/>
+        <v>19.8</v>
+      </c>
+      <c r="Q25" s="3">
+        <f t="shared" si="24"/>
+        <v>99</v>
+      </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26">
@@ -1669,23 +1929,48 @@
       <c r="C26" t="s">
         <v>65</v>
       </c>
+      <c r="D26">
+        <v>93</v>
+      </c>
       <c r="E26">
         <v>3</v>
       </c>
       <c r="K26">
         <f t="shared" si="6"/>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="2"/>
+        <v>19.8</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="19"/>
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="3">
+        <f t="shared" si="23"/>
+        <v>19.8</v>
+      </c>
+      <c r="Q26" s="3">
+        <f t="shared" si="24"/>
+        <v>99</v>
+      </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="1">
-        <f>AVERAGE(D6:D16)</f>
-        <v>85.7</v>
+        <f>AVERAGE(D6:D26)</f>
+        <v>89.15789473684211</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1" t="e">
@@ -1709,7 +1994,7 @@
       </c>
       <c r="Q28" s="2">
         <f>AVERAGE(Q6:Q16)</f>
-        <v>63.9</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -1717,8 +2002,8 @@
         <v>14</v>
       </c>
       <c r="D29" s="1">
-        <f>STDEV(D6:D16)</f>
-        <v>10.022751895340731</v>
+        <f>STDEV(D6:D26)</f>
+        <v>9.2512050740234386</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1" t="e">
@@ -1742,7 +2027,7 @@
       </c>
       <c r="Q29" s="2">
         <f>STDEV(Q6:Q16)</f>
-        <v>45.140398265362656</v>
+        <v>10.022751895340811</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -1750,7 +2035,7 @@
         <v>8</v>
       </c>
       <c r="D30">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
@@ -1764,15 +2049,15 @@
       </c>
       <c r="D32" s="1">
         <f>D28+D30+D31</f>
-        <v>89.7</v>
+        <v>92.15789473684211</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1" t="e">
-        <f t="shared" ref="F32:G32" si="8">F28+F30+F31</f>
+        <f t="shared" ref="F32:G32" si="25">F28+F30+F31</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G32" s="1" t="e">
-        <f t="shared" si="8"/>
+        <f t="shared" si="25"/>
         <v>#DIV/0!</v>
       </c>
       <c r="H32" s="1" t="e">
@@ -1892,10 +2177,22 @@
       <c r="Q37">
         <v>10</v>
       </c>
+      <c r="R37">
+        <v>9</v>
+      </c>
       <c r="S37">
         <v>10</v>
       </c>
       <c r="T37">
+        <v>10</v>
+      </c>
+      <c r="U37">
+        <v>10</v>
+      </c>
+      <c r="V37">
+        <v>10</v>
+      </c>
+      <c r="W37">
         <v>10</v>
       </c>
       <c r="X37">
@@ -1945,11 +2242,23 @@
       <c r="Q38">
         <v>12</v>
       </c>
+      <c r="R38">
+        <v>9</v>
+      </c>
       <c r="S38">
         <v>12</v>
       </c>
       <c r="T38">
         <v>12</v>
+      </c>
+      <c r="U38">
+        <v>12</v>
+      </c>
+      <c r="V38">
+        <v>12</v>
+      </c>
+      <c r="W38">
+        <v>10</v>
       </c>
       <c r="X38">
         <v>12</v>
@@ -1998,11 +2307,23 @@
       <c r="Q39">
         <v>8</v>
       </c>
+      <c r="R39">
+        <v>5</v>
+      </c>
       <c r="S39">
         <v>5</v>
       </c>
       <c r="T39">
         <v>6</v>
+      </c>
+      <c r="U39">
+        <v>5</v>
+      </c>
+      <c r="V39">
+        <v>8</v>
+      </c>
+      <c r="W39">
+        <v>5</v>
       </c>
       <c r="X39">
         <v>5</v>
@@ -2051,10 +2372,22 @@
       <c r="Q40">
         <v>18</v>
       </c>
+      <c r="R40">
+        <v>15</v>
+      </c>
       <c r="S40">
         <v>18</v>
       </c>
       <c r="T40">
+        <v>18</v>
+      </c>
+      <c r="U40">
+        <v>18</v>
+      </c>
+      <c r="V40">
+        <v>18</v>
+      </c>
+      <c r="W40">
         <v>18</v>
       </c>
       <c r="X40">
@@ -2104,10 +2437,22 @@
       <c r="Q41">
         <v>10</v>
       </c>
+      <c r="R41">
+        <v>6</v>
+      </c>
       <c r="S41">
         <v>8</v>
       </c>
       <c r="T41">
+        <v>9</v>
+      </c>
+      <c r="U41">
+        <v>10</v>
+      </c>
+      <c r="V41">
+        <v>10</v>
+      </c>
+      <c r="W41">
         <v>9</v>
       </c>
       <c r="X41">
@@ -2157,10 +2502,22 @@
       <c r="Q42">
         <v>18</v>
       </c>
+      <c r="R42">
+        <v>12</v>
+      </c>
       <c r="S42">
         <v>16</v>
       </c>
       <c r="T42">
+        <v>18</v>
+      </c>
+      <c r="U42">
+        <v>18</v>
+      </c>
+      <c r="V42">
+        <v>18</v>
+      </c>
+      <c r="W42">
         <v>18</v>
       </c>
       <c r="X42">
@@ -2210,10 +2567,22 @@
       <c r="Q43">
         <v>9</v>
       </c>
+      <c r="R43">
+        <v>9</v>
+      </c>
       <c r="S43">
         <v>9</v>
       </c>
       <c r="T43">
+        <v>9</v>
+      </c>
+      <c r="U43">
+        <v>9</v>
+      </c>
+      <c r="V43">
+        <v>9</v>
+      </c>
+      <c r="W43">
         <v>9</v>
       </c>
       <c r="X43">
@@ -2263,12 +2632,24 @@
       <c r="Q44">
         <v>5</v>
       </c>
+      <c r="R44">
+        <v>5</v>
+      </c>
       <c r="S44">
         <v>5</v>
       </c>
       <c r="T44">
         <v>5</v>
       </c>
+      <c r="U44">
+        <v>5</v>
+      </c>
+      <c r="V44">
+        <v>4</v>
+      </c>
+      <c r="W44">
+        <v>5</v>
+      </c>
       <c r="X44">
         <v>5</v>
       </c>
@@ -2316,10 +2697,22 @@
       <c r="Q45">
         <v>9</v>
       </c>
+      <c r="R45">
+        <v>6</v>
+      </c>
       <c r="S45">
         <v>8</v>
       </c>
       <c r="T45">
+        <v>9</v>
+      </c>
+      <c r="U45">
+        <v>9</v>
+      </c>
+      <c r="V45">
+        <v>10</v>
+      </c>
+      <c r="W45">
         <v>9</v>
       </c>
       <c r="X45">
@@ -2331,83 +2724,112 @@
         <v>12</v>
       </c>
       <c r="D46">
-        <f t="shared" ref="D46:N46" si="9">SUM(D37:D45)</f>
+        <f t="shared" ref="D46:N46" si="26">SUM(D37:D45)</f>
         <v>100</v>
       </c>
       <c r="E46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>74</v>
       </c>
       <c r="F46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>88</v>
       </c>
       <c r="G46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>97</v>
       </c>
       <c r="H46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>67</v>
       </c>
       <c r="I46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>81</v>
       </c>
       <c r="J46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>100</v>
       </c>
       <c r="K46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>83</v>
       </c>
       <c r="L46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>92</v>
       </c>
       <c r="M46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>89</v>
       </c>
       <c r="N46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="26"/>
         <v>86</v>
       </c>
       <c r="P46">
-        <f t="shared" ref="P46" si="10">SUM(P37:P45)</f>
+        <f t="shared" ref="P46" si="27">SUM(P37:P45)</f>
         <v>94</v>
       </c>
       <c r="Q46">
-        <f t="shared" ref="Q46" si="11">SUM(Q37:Q45)</f>
+        <f t="shared" ref="Q46" si="28">SUM(Q37:Q45)</f>
         <v>99</v>
       </c>
       <c r="R46">
-        <f t="shared" ref="R46" si="12">SUM(R37:R45)</f>
-        <v>0</v>
+        <f t="shared" ref="R46" si="29">SUM(R37:R45)</f>
+        <v>76</v>
       </c>
       <c r="S46">
-        <f t="shared" ref="S46" si="13">SUM(S37:S45)</f>
+        <f t="shared" ref="S46" si="30">SUM(S37:S45)</f>
         <v>91</v>
       </c>
       <c r="T46">
-        <f t="shared" ref="T46" si="14">SUM(T37:T45)</f>
+        <f t="shared" ref="T46" si="31">SUM(T37:T45)</f>
         <v>96</v>
       </c>
       <c r="U46">
-        <f t="shared" ref="U46" si="15">SUM(U37:U45)</f>
-        <v>0</v>
+        <f t="shared" ref="U46" si="32">SUM(U37:U45)</f>
+        <v>96</v>
       </c>
       <c r="V46">
-        <f t="shared" ref="V46" si="16">SUM(V37:V45)</f>
-        <v>0</v>
+        <f t="shared" ref="V46" si="33">SUM(V37:V45)</f>
+        <v>99</v>
       </c>
       <c r="W46">
-        <f t="shared" ref="W46" si="17">SUM(W37:W45)</f>
-        <v>0</v>
+        <f t="shared" ref="W46" si="34">SUM(W37:W45)</f>
+        <v>93</v>
       </c>
       <c r="X46">
-        <f t="shared" ref="X46" si="18">SUM(X37:X45)</f>
+        <f t="shared" ref="X46" si="35">SUM(X37:X45)</f>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="P48">
+        <v>94</v>
+      </c>
+      <c r="Q48">
+        <v>99</v>
+      </c>
+      <c r="R48">
+        <v>76</v>
+      </c>
+      <c r="S48">
+        <v>91</v>
+      </c>
+      <c r="T48">
+        <v>96</v>
+      </c>
+      <c r="U48">
+        <v>96</v>
+      </c>
+      <c r="V48">
+        <v>99</v>
+      </c>
+      <c r="W48">
+        <v>93</v>
+      </c>
+      <c r="X48">
         <v>93</v>
       </c>
     </row>

--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A837104-E7D2-BC40-9FCD-CA7BFFB30695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0149EBB4-6C60-BC4B-AE61-3B80B4B6230E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24120" yWindow="5440" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="5520" yWindow="4600" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="79">
   <si>
     <t>Roster</t>
   </si>
@@ -1013,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7A9E859-0099-8A4F-9892-6572C8559B21}">
-  <dimension ref="A2:X106"/>
+  <dimension ref="A2:X107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="20.1640625" customWidth="1"/>
@@ -2805,141 +2805,342 @@
       </c>
     </row>
     <row r="48" spans="3:24" x14ac:dyDescent="0.2">
-      <c r="P48">
-        <v>94</v>
-      </c>
-      <c r="Q48">
-        <v>99</v>
-      </c>
-      <c r="R48">
+      <c r="C48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>36</v>
+      </c>
+      <c r="H48" t="s">
+        <v>42</v>
+      </c>
+      <c r="I48" t="s">
+        <v>45</v>
+      </c>
+      <c r="J48" t="s">
+        <v>54</v>
+      </c>
+      <c r="K48" t="s">
+        <v>68</v>
+      </c>
+      <c r="L48" t="s">
+        <v>71</v>
+      </c>
+      <c r="M48" t="s">
+        <v>74</v>
+      </c>
+      <c r="N48" t="s">
         <v>76</v>
       </c>
-      <c r="S48">
-        <v>91</v>
-      </c>
-      <c r="T48">
-        <v>96</v>
-      </c>
-      <c r="U48">
-        <v>96</v>
-      </c>
-      <c r="V48">
-        <v>99</v>
-      </c>
-      <c r="W48">
-        <v>93</v>
-      </c>
-      <c r="X48">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="97" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D97" t="s">
-        <v>26</v>
-      </c>
-      <c r="E97" t="s">
-        <v>27</v>
-      </c>
-      <c r="F97" t="s">
-        <v>28</v>
+      <c r="P48" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>33</v>
+      </c>
+      <c r="R48" t="s">
+        <v>39</v>
+      </c>
+      <c r="S48" t="s">
+        <v>48</v>
+      </c>
+      <c r="T48" t="s">
+        <v>51</v>
+      </c>
+      <c r="U48" t="s">
+        <v>57</v>
+      </c>
+      <c r="V48" t="s">
+        <v>60</v>
+      </c>
+      <c r="W48" t="s">
+        <v>63</v>
+      </c>
+      <c r="X48" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C50">
+        <v>2</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C52">
+        <v>4</v>
+      </c>
+      <c r="D52">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C53">
+        <v>5</v>
+      </c>
+      <c r="D53">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C54">
+        <v>6</v>
+      </c>
+      <c r="D54">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C55">
+        <v>7</v>
+      </c>
+      <c r="D55">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C56">
+        <v>8</v>
+      </c>
+      <c r="D56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C57">
+        <v>9</v>
+      </c>
+      <c r="D57">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C58">
+        <v>10</v>
+      </c>
+      <c r="D58">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="C59" t="s">
+        <v>12</v>
+      </c>
+      <c r="D59">
+        <f>SUM(D49:D58)</f>
+        <v>100</v>
+      </c>
+      <c r="E59">
+        <f t="shared" ref="E59:P59" si="36">SUM(E49:E58)</f>
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <f t="shared" si="36"/>
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" ref="Q59" si="37">SUM(Q49:Q58)</f>
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <f t="shared" ref="R59" si="38">SUM(R49:R58)</f>
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <f t="shared" ref="S59" si="39">SUM(S49:S58)</f>
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <f t="shared" ref="T59" si="40">SUM(T49:T58)</f>
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <f t="shared" ref="U59" si="41">SUM(U49:U58)</f>
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <f t="shared" ref="V59" si="42">SUM(V49:V58)</f>
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <f t="shared" ref="W59" si="43">SUM(W49:W58)</f>
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <f t="shared" ref="X59" si="44">SUM(X49:X58)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D98" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E98" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F98" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="99" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D99" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F99" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="100" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D100" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E100" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F100" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="101" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D101" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E101" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F101" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="102" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D102" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E102" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F102" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="103" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D103" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E103" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F103" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D104" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E104" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F104" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="105" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D105" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E105" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F105" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="106" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D106" t="s">
+        <v>73</v>
+      </c>
+      <c r="E106" t="s">
+        <v>74</v>
+      </c>
+      <c r="F106" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="107" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D107" t="s">
         <v>23</v>
       </c>
-      <c r="E106" t="s">
+      <c r="E107" t="s">
         <v>76</v>
       </c>
-      <c r="F106" t="s">
+      <c r="F107" t="s">
         <v>77</v>
       </c>
     </row>

--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0149EBB4-6C60-BC4B-AE61-3B80B4B6230E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2596815F-BD9A-6943-94DB-814D6EA8BD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="4600" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -1047,6 +1047,9 @@
       <c r="D4">
         <v>0.2</v>
       </c>
+      <c r="F4">
+        <v>0.2</v>
+      </c>
       <c r="K4" t="s">
         <v>11</v>
       </c>
@@ -1114,13 +1117,16 @@
       <c r="E6">
         <v>3</v>
       </c>
+      <c r="F6">
+        <v>58</v>
+      </c>
       <c r="K6">
         <f>(D6+E6+D$30+D$31)*D$3</f>
         <v>16</v>
       </c>
       <c r="L6">
         <f>(F6+F$30+F$31)*F$3</f>
-        <v>0</v>
+        <v>11.600000000000001</v>
       </c>
       <c r="M6">
         <f t="shared" ref="M6:M12" si="0">(G6+G$30)*G$3</f>
@@ -1136,11 +1142,11 @@
       </c>
       <c r="P6" s="3">
         <f>SUM(K6:O6)</f>
-        <v>16</v>
+        <v>27.6</v>
       </c>
       <c r="Q6" s="3">
         <f>100*P6/(100*SUM($D$4:$I$4))</f>
-        <v>80</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
@@ -1159,13 +1165,16 @@
       <c r="E7">
         <v>3</v>
       </c>
+      <c r="F7">
+        <v>79</v>
+      </c>
       <c r="K7">
         <f>(D7+E7+D$30+D$31)*D$3</f>
         <v>18.8</v>
       </c>
       <c r="L7">
         <f t="shared" ref="L7:L12" si="3">(F7+F$30+F$31)*F$3</f>
-        <v>0</v>
+        <v>15.8</v>
       </c>
       <c r="M7">
         <f t="shared" si="0"/>
@@ -1181,11 +1190,11 @@
       </c>
       <c r="P7" s="3">
         <f t="shared" ref="P7:P12" si="4">SUM(K7:O7)</f>
-        <v>18.8</v>
+        <v>34.6</v>
       </c>
       <c r="Q7" s="3">
         <f t="shared" ref="Q7:Q15" si="5">100*P7/(100*SUM($D$4:$I$4))</f>
-        <v>94</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
@@ -1204,13 +1213,16 @@
       <c r="E8">
         <v>3</v>
       </c>
+      <c r="F8">
+        <v>94</v>
+      </c>
       <c r="K8">
         <f t="shared" ref="K8:K26" si="6">(D8+E8+D$30+D$31)*D$3</f>
         <v>20.6</v>
       </c>
       <c r="L8">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>18.8</v>
       </c>
       <c r="M8">
         <f t="shared" si="0"/>
@@ -1226,11 +1238,11 @@
       </c>
       <c r="P8" s="3">
         <f t="shared" ref="P8" si="7">SUM(K8:O8)</f>
-        <v>20.6</v>
+        <v>39.400000000000006</v>
       </c>
       <c r="Q8" s="3">
         <f t="shared" si="5"/>
-        <v>103</v>
+        <v>98.500000000000014</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
@@ -1249,13 +1261,16 @@
       <c r="E9">
         <v>3</v>
       </c>
+      <c r="F9">
+        <v>83</v>
+      </c>
       <c r="K9">
         <f t="shared" si="6"/>
         <v>14.600000000000001</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>16.600000000000001</v>
       </c>
       <c r="M9">
         <f t="shared" si="0"/>
@@ -1271,11 +1286,11 @@
       </c>
       <c r="P9" s="3">
         <f t="shared" si="4"/>
-        <v>14.600000000000001</v>
+        <v>31.200000000000003</v>
       </c>
       <c r="Q9" s="3">
         <f t="shared" si="5"/>
-        <v>73.000000000000014</v>
+        <v>78.000000000000014</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
@@ -1293,6 +1308,9 @@
       </c>
       <c r="E10">
         <v>3</v>
+      </c>
+      <c r="F10">
+        <v>98</v>
       </c>
       <c r="K10">
         <f t="shared" si="6"/>
@@ -1300,7 +1318,7 @@
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="M10">
         <f t="shared" si="0"/>
@@ -1316,11 +1334,11 @@
       </c>
       <c r="P10" s="3">
         <f t="shared" si="4"/>
-        <v>17.400000000000002</v>
+        <v>37</v>
       </c>
       <c r="Q10" s="3">
         <f t="shared" si="5"/>
-        <v>87.000000000000014</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
@@ -1365,7 +1383,7 @@
       </c>
       <c r="Q11" s="3">
         <f t="shared" si="5"/>
-        <v>106.00000000000003</v>
+        <v>53.000000000000014</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -1384,13 +1402,16 @@
       <c r="E12">
         <v>3</v>
       </c>
+      <c r="F12">
+        <v>88</v>
+      </c>
       <c r="K12">
         <f t="shared" si="6"/>
         <v>17.8</v>
       </c>
       <c r="L12">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>17.600000000000001</v>
       </c>
       <c r="M12">
         <f t="shared" si="0"/>
@@ -1406,11 +1427,11 @@
       </c>
       <c r="P12" s="3">
         <f t="shared" si="4"/>
-        <v>17.8</v>
+        <v>35.400000000000006</v>
       </c>
       <c r="Q12" s="3">
         <f t="shared" si="5"/>
-        <v>89</v>
+        <v>88.500000000000014</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
@@ -1429,13 +1450,16 @@
       <c r="E13">
         <v>3</v>
       </c>
+      <c r="F13">
+        <v>98</v>
+      </c>
       <c r="K13">
         <f t="shared" si="6"/>
         <v>19.600000000000001</v>
       </c>
       <c r="L13">
         <f t="shared" ref="L13:L15" si="8">(F13+F$30+F$31)*F$3</f>
-        <v>0</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="M13">
         <f t="shared" ref="M13:M15" si="9">(G13+G$30)*G$3</f>
@@ -1451,7 +1475,7 @@
       </c>
       <c r="P13" s="3">
         <f t="shared" ref="P13:P15" si="12">SUM(K13:O13)</f>
-        <v>19.600000000000001</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="Q13" s="3">
         <f t="shared" si="5"/>
@@ -1500,7 +1524,7 @@
       </c>
       <c r="Q14" s="3">
         <f t="shared" si="5"/>
-        <v>95</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
@@ -1518,6 +1542,9 @@
       </c>
       <c r="E15">
         <v>3</v>
+      </c>
+      <c r="F15">
+        <v>96</v>
       </c>
       <c r="K15">
         <f t="shared" si="6"/>
@@ -1525,7 +1552,7 @@
       </c>
       <c r="L15">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19.200000000000003</v>
       </c>
       <c r="M15">
         <f t="shared" si="9"/>
@@ -1541,11 +1568,11 @@
       </c>
       <c r="P15" s="3">
         <f t="shared" si="12"/>
-        <v>18.400000000000002</v>
+        <v>37.600000000000009</v>
       </c>
       <c r="Q15" s="3">
         <f t="shared" si="5"/>
-        <v>92.000000000000014</v>
+        <v>94.000000000000028</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
@@ -1601,7 +1628,7 @@
       </c>
       <c r="Q18" s="3">
         <f t="shared" ref="Q18" si="18">100*P18/(100*SUM($D$4:$I$4))</f>
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
@@ -1646,7 +1673,7 @@
       </c>
       <c r="Q19" s="3">
         <f t="shared" ref="Q19:Q26" si="24">100*P19/(100*SUM($D$4:$I$4))</f>
-        <v>105</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
@@ -1691,7 +1718,7 @@
       </c>
       <c r="Q20" s="3">
         <f t="shared" si="24"/>
-        <v>82.000000000000014</v>
+        <v>41.000000000000007</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
@@ -1710,13 +1737,16 @@
       <c r="E21">
         <v>3</v>
       </c>
+      <c r="F21">
+        <v>95</v>
+      </c>
       <c r="K21">
         <f t="shared" si="6"/>
         <v>19.400000000000002</v>
       </c>
       <c r="L21">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M21">
         <f t="shared" si="20"/>
@@ -1732,11 +1762,11 @@
       </c>
       <c r="P21" s="3">
         <f t="shared" si="23"/>
-        <v>19.400000000000002</v>
+        <v>38.400000000000006</v>
       </c>
       <c r="Q21" s="3">
         <f t="shared" si="24"/>
-        <v>97.000000000000014</v>
+        <v>96.000000000000014</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
@@ -1781,7 +1811,7 @@
       </c>
       <c r="Q22" s="3">
         <f t="shared" si="24"/>
-        <v>102.00000000000001</v>
+        <v>51.000000000000007</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
@@ -1826,7 +1856,7 @@
       </c>
       <c r="Q23" s="3">
         <f t="shared" si="24"/>
-        <v>102.00000000000001</v>
+        <v>51.000000000000007</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
@@ -1871,7 +1901,7 @@
       </c>
       <c r="Q24" s="3">
         <f t="shared" si="24"/>
-        <v>105</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
@@ -1890,13 +1920,16 @@
       <c r="E25">
         <v>3</v>
       </c>
+      <c r="F25">
+        <v>99</v>
+      </c>
       <c r="K25">
         <f t="shared" si="6"/>
         <v>19.8</v>
       </c>
       <c r="L25">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="M25">
         <f t="shared" si="20"/>
@@ -1912,7 +1945,7 @@
       </c>
       <c r="P25" s="3">
         <f t="shared" si="23"/>
-        <v>19.8</v>
+        <v>39.6</v>
       </c>
       <c r="Q25" s="3">
         <f t="shared" si="24"/>
@@ -1961,7 +1994,7 @@
       </c>
       <c r="Q26" s="3">
         <f t="shared" si="24"/>
-        <v>99</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
@@ -1973,9 +2006,9 @@
         <v>89.15789473684211</v>
       </c>
       <c r="E28" s="1"/>
-      <c r="F28" s="1" t="e">
+      <c r="F28" s="1">
         <f>AVERAGE(F6:F16)</f>
-        <v>#DIV/0!</v>
+        <v>86.75</v>
       </c>
       <c r="G28" s="1" t="e">
         <f>AVERAGE(G6:G16)</f>
@@ -1994,7 +2027,7 @@
       </c>
       <c r="Q28" s="2">
         <f>AVERAGE(Q6:Q16)</f>
-        <v>91.7</v>
+        <v>80.55</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -2006,9 +2039,9 @@
         <v>9.2512050740234386</v>
       </c>
       <c r="E29" s="1"/>
-      <c r="F29" s="1" t="e">
+      <c r="F29" s="1">
         <f>STDEV(F6:F16)</f>
-        <v>#DIV/0!</v>
+        <v>13.593590926819678</v>
       </c>
       <c r="G29" s="1" t="e">
         <f>STDEV(G6:G16)</f>
@@ -2027,7 +2060,7 @@
       </c>
       <c r="Q29" s="2">
         <f>STDEV(Q6:Q16)</f>
-        <v>10.022751895340811</v>
+        <v>18.379411790853897</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -2052,9 +2085,9 @@
         <v>92.15789473684211</v>
       </c>
       <c r="E32" s="1"/>
-      <c r="F32" s="1" t="e">
+      <c r="F32" s="1">
         <f t="shared" ref="F32:G32" si="25">F28+F30+F31</f>
-        <v>#DIV/0!</v>
+        <v>86.75</v>
       </c>
       <c r="G32" s="1" t="e">
         <f t="shared" si="25"/>
@@ -2876,6 +2909,36 @@
       <c r="D49">
         <v>6</v>
       </c>
+      <c r="E49">
+        <v>6</v>
+      </c>
+      <c r="F49">
+        <v>4</v>
+      </c>
+      <c r="G49">
+        <v>6</v>
+      </c>
+      <c r="H49">
+        <v>6</v>
+      </c>
+      <c r="I49">
+        <v>5</v>
+      </c>
+      <c r="K49">
+        <v>6</v>
+      </c>
+      <c r="L49">
+        <v>5</v>
+      </c>
+      <c r="N49">
+        <v>6</v>
+      </c>
+      <c r="S49">
+        <v>6</v>
+      </c>
+      <c r="W49">
+        <v>5</v>
+      </c>
     </row>
     <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50">
@@ -2884,6 +2947,36 @@
       <c r="D50">
         <v>6</v>
       </c>
+      <c r="E50">
+        <v>5</v>
+      </c>
+      <c r="F50">
+        <v>5</v>
+      </c>
+      <c r="G50">
+        <v>5</v>
+      </c>
+      <c r="H50">
+        <v>5</v>
+      </c>
+      <c r="I50">
+        <v>6</v>
+      </c>
+      <c r="K50">
+        <v>6</v>
+      </c>
+      <c r="L50">
+        <v>6</v>
+      </c>
+      <c r="N50">
+        <v>5</v>
+      </c>
+      <c r="S50">
+        <v>6</v>
+      </c>
+      <c r="W50">
+        <v>6</v>
+      </c>
     </row>
     <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51">
@@ -2892,6 +2985,36 @@
       <c r="D51">
         <v>10</v>
       </c>
+      <c r="E51">
+        <v>6</v>
+      </c>
+      <c r="F51">
+        <v>10</v>
+      </c>
+      <c r="G51">
+        <v>10</v>
+      </c>
+      <c r="H51">
+        <v>8</v>
+      </c>
+      <c r="I51">
+        <v>10</v>
+      </c>
+      <c r="K51">
+        <v>10</v>
+      </c>
+      <c r="L51">
+        <v>10</v>
+      </c>
+      <c r="N51">
+        <v>9</v>
+      </c>
+      <c r="S51">
+        <v>7</v>
+      </c>
+      <c r="W51">
+        <v>10</v>
+      </c>
     </row>
     <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52">
@@ -2900,12 +3023,72 @@
       <c r="D52">
         <v>14</v>
       </c>
+      <c r="E52">
+        <v>5</v>
+      </c>
+      <c r="F52">
+        <v>9</v>
+      </c>
+      <c r="G52">
+        <v>10</v>
+      </c>
+      <c r="H52">
+        <v>10</v>
+      </c>
+      <c r="I52">
+        <v>14</v>
+      </c>
+      <c r="K52">
+        <v>11</v>
+      </c>
+      <c r="L52">
+        <v>14</v>
+      </c>
+      <c r="N52">
+        <v>12</v>
+      </c>
+      <c r="S52">
+        <v>14</v>
+      </c>
+      <c r="W52">
+        <v>14</v>
+      </c>
     </row>
     <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53">
         <v>5</v>
       </c>
       <c r="D53">
+        <v>8</v>
+      </c>
+      <c r="E53">
+        <v>7</v>
+      </c>
+      <c r="F53">
+        <v>7</v>
+      </c>
+      <c r="G53">
+        <v>8</v>
+      </c>
+      <c r="H53">
+        <v>8</v>
+      </c>
+      <c r="I53">
+        <v>8</v>
+      </c>
+      <c r="K53">
+        <v>8</v>
+      </c>
+      <c r="L53">
+        <v>8</v>
+      </c>
+      <c r="N53">
+        <v>8</v>
+      </c>
+      <c r="S53">
+        <v>8</v>
+      </c>
+      <c r="W53">
         <v>8</v>
       </c>
     </row>
@@ -2916,6 +3099,36 @@
       <c r="D54">
         <v>14</v>
       </c>
+      <c r="E54">
+        <v>7</v>
+      </c>
+      <c r="F54">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>13</v>
+      </c>
+      <c r="H54">
+        <v>11</v>
+      </c>
+      <c r="I54">
+        <v>13</v>
+      </c>
+      <c r="K54">
+        <v>11</v>
+      </c>
+      <c r="L54">
+        <v>14</v>
+      </c>
+      <c r="N54">
+        <v>14</v>
+      </c>
+      <c r="S54">
+        <v>13</v>
+      </c>
+      <c r="W54">
+        <v>14</v>
+      </c>
     </row>
     <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55">
@@ -2924,6 +3137,36 @@
       <c r="D55">
         <v>12</v>
       </c>
+      <c r="E55">
+        <v>5</v>
+      </c>
+      <c r="F55">
+        <v>4</v>
+      </c>
+      <c r="G55">
+        <v>12</v>
+      </c>
+      <c r="H55">
+        <v>11</v>
+      </c>
+      <c r="I55">
+        <v>12</v>
+      </c>
+      <c r="K55">
+        <v>11</v>
+      </c>
+      <c r="L55">
+        <v>12</v>
+      </c>
+      <c r="N55">
+        <v>12</v>
+      </c>
+      <c r="S55">
+        <v>11</v>
+      </c>
+      <c r="W55">
+        <v>12</v>
+      </c>
     </row>
     <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56">
@@ -2932,6 +3175,36 @@
       <c r="D56">
         <v>10</v>
       </c>
+      <c r="E56">
+        <v>5</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56">
+        <v>10</v>
+      </c>
+      <c r="H56">
+        <v>9</v>
+      </c>
+      <c r="I56">
+        <v>10</v>
+      </c>
+      <c r="K56">
+        <v>7</v>
+      </c>
+      <c r="L56">
+        <v>9</v>
+      </c>
+      <c r="N56">
+        <v>10</v>
+      </c>
+      <c r="S56">
+        <v>10</v>
+      </c>
+      <c r="W56">
+        <v>10</v>
+      </c>
     </row>
     <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57">
@@ -2940,12 +3213,72 @@
       <c r="D57">
         <v>12</v>
       </c>
+      <c r="E57">
+        <v>7</v>
+      </c>
+      <c r="F57">
+        <v>12</v>
+      </c>
+      <c r="G57">
+        <v>12</v>
+      </c>
+      <c r="H57">
+        <v>9</v>
+      </c>
+      <c r="I57">
+        <v>12</v>
+      </c>
+      <c r="K57">
+        <v>12</v>
+      </c>
+      <c r="L57">
+        <v>12</v>
+      </c>
+      <c r="N57">
+        <v>12</v>
+      </c>
+      <c r="S57">
+        <v>12</v>
+      </c>
+      <c r="W57">
+        <v>12</v>
+      </c>
     </row>
     <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58">
         <v>10</v>
       </c>
       <c r="D58">
+        <v>8</v>
+      </c>
+      <c r="E58">
+        <v>5</v>
+      </c>
+      <c r="F58">
+        <v>7</v>
+      </c>
+      <c r="G58">
+        <v>8</v>
+      </c>
+      <c r="H58">
+        <v>6</v>
+      </c>
+      <c r="I58">
+        <v>8</v>
+      </c>
+      <c r="K58">
+        <v>6</v>
+      </c>
+      <c r="L58">
+        <v>8</v>
+      </c>
+      <c r="N58">
+        <v>8</v>
+      </c>
+      <c r="S58">
+        <v>8</v>
+      </c>
+      <c r="W58">
         <v>8</v>
       </c>
     </row>
@@ -2959,23 +3292,23 @@
       </c>
       <c r="E59">
         <f t="shared" ref="E59:P59" si="36">SUM(E49:E58)</f>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="H59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="I59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="J59">
         <f t="shared" si="36"/>
@@ -2983,11 +3316,11 @@
       </c>
       <c r="K59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="L59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="M59">
         <f t="shared" si="36"/>
@@ -2995,7 +3328,7 @@
       </c>
       <c r="N59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="P59">
         <f t="shared" si="36"/>
@@ -3011,7 +3344,7 @@
       </c>
       <c r="S59">
         <f t="shared" ref="S59" si="39">SUM(S49:S58)</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="T59">
         <f t="shared" ref="T59" si="40">SUM(T49:T58)</f>
@@ -3027,7 +3360,7 @@
       </c>
       <c r="W59">
         <f t="shared" ref="W59" si="43">SUM(W49:W58)</f>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="X59">
         <f t="shared" ref="X59" si="44">SUM(X49:X58)</f>

--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr showObjects="none" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2596815F-BD9A-6943-94DB-814D6EA8BD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D62988-4E66-874D-AE60-110BC7E95F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5520" yWindow="4600" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
+    <workbookView xWindow="5520" yWindow="3820" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
   <sheets>
     <sheet name="Contacts" sheetId="2" r:id="rId1"/>
@@ -1357,13 +1357,16 @@
       <c r="E11">
         <v>3</v>
       </c>
+      <c r="F11">
+        <v>99</v>
+      </c>
       <c r="K11">
         <f t="shared" si="6"/>
         <v>21.200000000000003</v>
       </c>
       <c r="L11">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="M11">
         <f t="shared" si="0"/>
@@ -1379,11 +1382,11 @@
       </c>
       <c r="P11" s="3">
         <f t="shared" si="4"/>
-        <v>21.200000000000003</v>
+        <v>41</v>
       </c>
       <c r="Q11" s="3">
         <f t="shared" si="5"/>
-        <v>53.000000000000014</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
@@ -2008,7 +2011,7 @@
       <c r="E28" s="1"/>
       <c r="F28" s="1">
         <f>AVERAGE(F6:F16)</f>
-        <v>86.75</v>
+        <v>88.111111111111114</v>
       </c>
       <c r="G28" s="1" t="e">
         <f>AVERAGE(G6:G16)</f>
@@ -2027,7 +2030,7 @@
       </c>
       <c r="Q28" s="2">
         <f>AVERAGE(Q6:Q16)</f>
-        <v>80.55</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -2041,7 +2044,7 @@
       <c r="E29" s="1"/>
       <c r="F29" s="1">
         <f>STDEV(F6:F16)</f>
-        <v>13.593590926819678</v>
+        <v>13.355190418377093</v>
       </c>
       <c r="G29" s="1" t="e">
         <f>STDEV(G6:G16)</f>
@@ -2060,7 +2063,7 @@
       </c>
       <c r="Q29" s="2">
         <f>STDEV(Q6:Q16)</f>
-        <v>18.379411790853897</v>
+        <v>16.726559053725886</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -2087,7 +2090,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1">
         <f t="shared" ref="F32:G32" si="25">F28+F30+F31</f>
-        <v>86.75</v>
+        <v>88.111111111111114</v>
       </c>
       <c r="G32" s="1" t="e">
         <f t="shared" si="25"/>
@@ -2924,6 +2927,9 @@
       <c r="I49">
         <v>5</v>
       </c>
+      <c r="J49">
+        <v>5</v>
+      </c>
       <c r="K49">
         <v>6</v>
       </c>
@@ -2933,11 +2939,20 @@
       <c r="N49">
         <v>6</v>
       </c>
+      <c r="Q49">
+        <v>6</v>
+      </c>
       <c r="S49">
         <v>6</v>
       </c>
+      <c r="T49">
+        <v>6</v>
+      </c>
       <c r="W49">
         <v>5</v>
+      </c>
+      <c r="X49">
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="3:24" x14ac:dyDescent="0.2">
@@ -2962,6 +2977,9 @@
       <c r="I50">
         <v>6</v>
       </c>
+      <c r="J50">
+        <v>6</v>
+      </c>
       <c r="K50">
         <v>6</v>
       </c>
@@ -2971,10 +2989,19 @@
       <c r="N50">
         <v>5</v>
       </c>
+      <c r="Q50">
+        <v>6</v>
+      </c>
       <c r="S50">
         <v>6</v>
       </c>
+      <c r="T50">
+        <v>6</v>
+      </c>
       <c r="W50">
+        <v>6</v>
+      </c>
+      <c r="X50">
         <v>6</v>
       </c>
     </row>
@@ -3000,6 +3027,9 @@
       <c r="I51">
         <v>10</v>
       </c>
+      <c r="J51">
+        <v>10</v>
+      </c>
       <c r="K51">
         <v>10</v>
       </c>
@@ -3007,12 +3037,21 @@
         <v>10</v>
       </c>
       <c r="N51">
+        <v>9</v>
+      </c>
+      <c r="Q51">
         <v>9</v>
       </c>
       <c r="S51">
         <v>7</v>
       </c>
+      <c r="T51">
+        <v>10</v>
+      </c>
       <c r="W51">
+        <v>10</v>
+      </c>
+      <c r="X51">
         <v>10</v>
       </c>
     </row>
@@ -3038,6 +3077,9 @@
       <c r="I52">
         <v>14</v>
       </c>
+      <c r="J52">
+        <v>14</v>
+      </c>
       <c r="K52">
         <v>11</v>
       </c>
@@ -3047,12 +3089,21 @@
       <c r="N52">
         <v>12</v>
       </c>
+      <c r="Q52">
+        <v>13</v>
+      </c>
       <c r="S52">
         <v>14</v>
       </c>
+      <c r="T52">
+        <v>14</v>
+      </c>
       <c r="W52">
         <v>14</v>
       </c>
+      <c r="X52">
+        <v>12</v>
+      </c>
     </row>
     <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53">
@@ -3076,6 +3127,9 @@
       <c r="I53">
         <v>8</v>
       </c>
+      <c r="J53">
+        <v>8</v>
+      </c>
       <c r="K53">
         <v>8</v>
       </c>
@@ -3085,10 +3139,19 @@
       <c r="N53">
         <v>8</v>
       </c>
+      <c r="Q53">
+        <v>8</v>
+      </c>
       <c r="S53">
         <v>8</v>
       </c>
+      <c r="T53">
+        <v>8</v>
+      </c>
       <c r="W53">
+        <v>8</v>
+      </c>
+      <c r="X53">
         <v>8</v>
       </c>
     </row>
@@ -3114,6 +3177,9 @@
       <c r="I54">
         <v>13</v>
       </c>
+      <c r="J54">
+        <v>14</v>
+      </c>
       <c r="K54">
         <v>11</v>
       </c>
@@ -3123,10 +3189,19 @@
       <c r="N54">
         <v>14</v>
       </c>
+      <c r="Q54">
+        <v>14</v>
+      </c>
       <c r="S54">
         <v>13</v>
       </c>
+      <c r="T54">
+        <v>14</v>
+      </c>
       <c r="W54">
+        <v>14</v>
+      </c>
+      <c r="X54">
         <v>14</v>
       </c>
     </row>
@@ -3152,6 +3227,9 @@
       <c r="I55">
         <v>12</v>
       </c>
+      <c r="J55">
+        <v>12</v>
+      </c>
       <c r="K55">
         <v>11</v>
       </c>
@@ -3161,10 +3239,19 @@
       <c r="N55">
         <v>12</v>
       </c>
+      <c r="Q55">
+        <v>12</v>
+      </c>
       <c r="S55">
         <v>11</v>
       </c>
+      <c r="T55">
+        <v>11</v>
+      </c>
       <c r="W55">
+        <v>12</v>
+      </c>
+      <c r="X55">
         <v>12</v>
       </c>
     </row>
@@ -3190,6 +3277,9 @@
       <c r="I56">
         <v>10</v>
       </c>
+      <c r="J56">
+        <v>10</v>
+      </c>
       <c r="K56">
         <v>7</v>
       </c>
@@ -3199,11 +3289,20 @@
       <c r="N56">
         <v>10</v>
       </c>
+      <c r="Q56">
+        <v>7</v>
+      </c>
       <c r="S56">
         <v>10</v>
       </c>
+      <c r="T56">
+        <v>9</v>
+      </c>
       <c r="W56">
         <v>10</v>
+      </c>
+      <c r="X56">
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="3:24" x14ac:dyDescent="0.2">
@@ -3228,6 +3327,9 @@
       <c r="I57">
         <v>12</v>
       </c>
+      <c r="J57">
+        <v>12</v>
+      </c>
       <c r="K57">
         <v>12</v>
       </c>
@@ -3237,10 +3339,19 @@
       <c r="N57">
         <v>12</v>
       </c>
+      <c r="Q57">
+        <v>11</v>
+      </c>
       <c r="S57">
         <v>12</v>
       </c>
+      <c r="T57">
+        <v>11</v>
+      </c>
       <c r="W57">
+        <v>12</v>
+      </c>
+      <c r="X57">
         <v>12</v>
       </c>
     </row>
@@ -3266,6 +3377,9 @@
       <c r="I58">
         <v>8</v>
       </c>
+      <c r="J58">
+        <v>8</v>
+      </c>
       <c r="K58">
         <v>6</v>
       </c>
@@ -3275,11 +3389,20 @@
       <c r="N58">
         <v>8</v>
       </c>
+      <c r="Q58">
+        <v>6</v>
+      </c>
       <c r="S58">
         <v>8</v>
       </c>
+      <c r="T58">
+        <v>8</v>
+      </c>
       <c r="W58">
         <v>8</v>
+      </c>
+      <c r="X58">
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="3:24" x14ac:dyDescent="0.2">
@@ -3312,7 +3435,7 @@
       </c>
       <c r="J59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="K59">
         <f t="shared" si="36"/>
@@ -3336,7 +3459,7 @@
       </c>
       <c r="Q59">
         <f t="shared" ref="Q59" si="37">SUM(Q49:Q58)</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="R59">
         <f t="shared" ref="R59" si="38">SUM(R49:R58)</f>
@@ -3348,7 +3471,7 @@
       </c>
       <c r="T59">
         <f t="shared" ref="T59" si="40">SUM(T49:T58)</f>
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="U59">
         <f t="shared" ref="U59" si="41">SUM(U49:U58)</f>
@@ -3364,7 +3487,7 @@
       </c>
       <c r="X59">
         <f t="shared" ref="X59" si="44">SUM(X49:X58)</f>
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="98" spans="4:6" x14ac:dyDescent="0.2">

--- a/Advanced Reactor Materials/Fall2026/grading.xlsx
+++ b/Advanced Reactor Materials/Fall2026/grading.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr showObjects="none" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/projects/TEACHING/Advanced Reactor Materials/Fall2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52D62988-4E66-874D-AE60-110BC7E95F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{722694A8-9A12-384A-8842-FC2EA42F17DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5520" yWindow="3820" windowWidth="24220" windowHeight="17440" activeTab="1" xr2:uid="{4E6CEA4E-2509-754B-9890-44C713F10933}"/>
   </bookViews>
@@ -1525,10 +1525,7 @@
         <f t="shared" si="12"/>
         <v>19</v>
       </c>
-      <c r="Q14" s="3">
-        <f t="shared" si="5"/>
-        <v>47.5</v>
-      </c>
+      <c r="Q14" s="3"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15">
@@ -1605,13 +1602,16 @@
       <c r="E18">
         <v>3</v>
       </c>
+      <c r="F18">
+        <v>99</v>
+      </c>
       <c r="K18">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="L18">
         <f t="shared" ref="L18" si="13">(F18+F$30+F$31)*F$3</f>
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="M18">
         <f t="shared" ref="M18" si="14">(G18+G$30)*G$3</f>
@@ -1627,11 +1627,11 @@
       </c>
       <c r="P18" s="3">
         <f t="shared" ref="P18" si="17">SUM(K18:O18)</f>
-        <v>20</v>
+        <v>39.799999999999997</v>
       </c>
       <c r="Q18" s="3">
         <f t="shared" ref="Q18" si="18">100*P18/(100*SUM($D$4:$I$4))</f>
-        <v>50</v>
+        <v>99.499999999999986</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
@@ -1649,6 +1649,9 @@
       </c>
       <c r="E19">
         <v>3</v>
+      </c>
+      <c r="F19">
+        <v>92</v>
       </c>
       <c r="K19">
         <f t="shared" si="6"/>
@@ -1656,7 +1659,7 @@
       </c>
       <c r="L19">
         <f t="shared" ref="L19:L26" si="19">(F19+F$30+F$31)*F$3</f>
-        <v>0</v>
+        <v>18.400000000000002</v>
       </c>
       <c r="M19">
         <f t="shared" ref="M19:M26" si="20">(G19+G$30)*G$3</f>
@@ -1672,11 +1675,11 @@
       </c>
       <c r="P19" s="3">
         <f t="shared" ref="P19:P26" si="23">SUM(K19:O19)</f>
-        <v>21</v>
+        <v>39.400000000000006</v>
       </c>
       <c r="Q19" s="3">
         <f t="shared" ref="Q19:Q26" si="24">100*P19/(100*SUM($D$4:$I$4))</f>
-        <v>52.5</v>
+        <v>98.500000000000014</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
@@ -1695,13 +1698,16 @@
       <c r="E20">
         <v>3</v>
       </c>
+      <c r="F20">
+        <v>82</v>
+      </c>
       <c r="K20">
         <f t="shared" si="6"/>
         <v>16.400000000000002</v>
       </c>
       <c r="L20">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>16.400000000000002</v>
       </c>
       <c r="M20">
         <f t="shared" si="20"/>
@@ -1717,11 +1723,11 @@
       </c>
       <c r="P20" s="3">
         <f t="shared" si="23"/>
-        <v>16.400000000000002</v>
+        <v>32.800000000000004</v>
       </c>
       <c r="Q20" s="3">
         <f t="shared" si="24"/>
-        <v>41.000000000000007</v>
+        <v>82.000000000000014</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
@@ -1788,13 +1794,16 @@
       <c r="E22">
         <v>3</v>
       </c>
+      <c r="F22">
+        <v>97</v>
+      </c>
       <c r="K22">
         <f t="shared" si="6"/>
         <v>20.400000000000002</v>
       </c>
       <c r="L22">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>19.400000000000002</v>
       </c>
       <c r="M22">
         <f t="shared" si="20"/>
@@ -1810,11 +1819,11 @@
       </c>
       <c r="P22" s="3">
         <f t="shared" si="23"/>
-        <v>20.400000000000002</v>
+        <v>39.800000000000004</v>
       </c>
       <c r="Q22" s="3">
         <f t="shared" si="24"/>
-        <v>51.000000000000007</v>
+        <v>99.500000000000014</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
@@ -1833,13 +1842,16 @@
       <c r="E23">
         <v>3</v>
       </c>
+      <c r="F23">
+        <v>98</v>
+      </c>
       <c r="K23">
         <f t="shared" si="6"/>
         <v>20.400000000000002</v>
       </c>
       <c r="L23">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="M23">
         <f t="shared" si="20"/>
@@ -1855,11 +1867,11 @@
       </c>
       <c r="P23" s="3">
         <f t="shared" si="23"/>
-        <v>20.400000000000002</v>
+        <v>40</v>
       </c>
       <c r="Q23" s="3">
         <f t="shared" si="24"/>
-        <v>51.000000000000007</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
@@ -1878,13 +1890,16 @@
       <c r="E24">
         <v>3</v>
       </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
       <c r="K24">
         <f t="shared" si="6"/>
         <v>21</v>
       </c>
       <c r="L24">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M24">
         <f t="shared" si="20"/>
@@ -1900,11 +1915,11 @@
       </c>
       <c r="P24" s="3">
         <f t="shared" si="23"/>
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="Q24" s="3">
         <f t="shared" si="24"/>
-        <v>52.5</v>
+        <v>102.5</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
@@ -1971,13 +1986,16 @@
       <c r="E26">
         <v>3</v>
       </c>
+      <c r="F26">
+        <v>96</v>
+      </c>
       <c r="K26">
         <f t="shared" si="6"/>
         <v>19.8</v>
       </c>
       <c r="L26">
         <f t="shared" si="19"/>
-        <v>0</v>
+        <v>19.200000000000003</v>
       </c>
       <c r="M26">
         <f t="shared" si="20"/>
@@ -1993,11 +2011,11 @@
       </c>
       <c r="P26" s="3">
         <f t="shared" si="23"/>
-        <v>19.8</v>
+        <v>39</v>
       </c>
       <c r="Q26" s="3">
         <f t="shared" si="24"/>
-        <v>49.5</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
@@ -2010,8 +2028,8 @@
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1">
-        <f>AVERAGE(F6:F16)</f>
-        <v>88.111111111111114</v>
+        <f>AVERAGE(F6:F26)</f>
+        <v>91.722222222222229</v>
       </c>
       <c r="G28" s="1" t="e">
         <f>AVERAGE(G6:G16)</f>
@@ -2029,8 +2047,8 @@
         <v>15</v>
       </c>
       <c r="Q28" s="2">
-        <f>AVERAGE(Q6:Q16)</f>
-        <v>85.5</v>
+        <f>AVERAGE(Q6:Q26)</f>
+        <v>93.444444444444443</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -2043,8 +2061,8 @@
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="1">
-        <f>STDEV(F6:F16)</f>
-        <v>13.355190418377093</v>
+        <f>STDEV(F6:F26)</f>
+        <v>10.598587894596047</v>
       </c>
       <c r="G29" s="1" t="e">
         <f>STDEV(G6:G16)</f>
@@ -2062,8 +2080,8 @@
         <v>16</v>
       </c>
       <c r="Q29" s="2">
-        <f>STDEV(Q6:Q16)</f>
-        <v>16.726559053725886</v>
+        <f>STDEV(Q6:Q26)</f>
+        <v>9.2257454487411081</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -2090,7 +2108,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1">
         <f t="shared" ref="F32:G32" si="25">F28+F30+F31</f>
-        <v>88.111111111111114</v>
+        <v>91.722222222222229</v>
       </c>
       <c r="G32" s="1" t="e">
         <f t="shared" si="25"/>
@@ -2939,13 +2957,25 @@
       <c r="N49">
         <v>6</v>
       </c>
+      <c r="P49">
+        <v>6</v>
+      </c>
       <c r="Q49">
         <v>6</v>
       </c>
+      <c r="R49">
+        <v>6</v>
+      </c>
       <c r="S49">
         <v>6</v>
       </c>
       <c r="T49">
+        <v>6</v>
+      </c>
+      <c r="U49">
+        <v>6</v>
+      </c>
+      <c r="V49">
         <v>6</v>
       </c>
       <c r="W49">
@@ -2989,13 +3019,25 @@
       <c r="N50">
         <v>5</v>
       </c>
+      <c r="P50">
+        <v>6</v>
+      </c>
       <c r="Q50">
         <v>6</v>
       </c>
+      <c r="R50">
+        <v>4</v>
+      </c>
       <c r="S50">
         <v>6</v>
       </c>
       <c r="T50">
+        <v>6</v>
+      </c>
+      <c r="U50">
+        <v>6</v>
+      </c>
+      <c r="V50">
         <v>6</v>
       </c>
       <c r="W50">
@@ -3039,13 +3081,25 @@
       <c r="N51">
         <v>9</v>
       </c>
+      <c r="P51">
+        <v>10</v>
+      </c>
       <c r="Q51">
+        <v>9</v>
+      </c>
+      <c r="R51">
         <v>9</v>
       </c>
       <c r="S51">
         <v>7</v>
       </c>
       <c r="T51">
+        <v>10</v>
+      </c>
+      <c r="U51">
+        <v>9</v>
+      </c>
+      <c r="V51">
         <v>10</v>
       </c>
       <c r="W51">
@@ -3089,15 +3143,27 @@
       <c r="N52">
         <v>12</v>
       </c>
+      <c r="P52">
+        <v>14</v>
+      </c>
       <c r="Q52">
         <v>13</v>
       </c>
+      <c r="R52">
+        <v>12</v>
+      </c>
       <c r="S52">
         <v>14</v>
       </c>
       <c r="T52">
         <v>14</v>
       </c>
+      <c r="U52">
+        <v>14</v>
+      </c>
+      <c r="V52">
+        <v>14</v>
+      </c>
       <c r="W52">
         <v>14</v>
       </c>
@@ -3139,13 +3205,25 @@
       <c r="N53">
         <v>8</v>
       </c>
+      <c r="P53">
+        <v>8</v>
+      </c>
       <c r="Q53">
         <v>8</v>
       </c>
+      <c r="R53">
+        <v>8</v>
+      </c>
       <c r="S53">
         <v>8</v>
       </c>
       <c r="T53">
+        <v>8</v>
+      </c>
+      <c r="U53">
+        <v>8</v>
+      </c>
+      <c r="V53">
         <v>8</v>
       </c>
       <c r="W53">
@@ -3189,13 +3267,25 @@
       <c r="N54">
         <v>14</v>
       </c>
+      <c r="P54">
+        <v>14</v>
+      </c>
       <c r="Q54">
         <v>14</v>
       </c>
+      <c r="R54">
+        <v>10</v>
+      </c>
       <c r="S54">
         <v>13</v>
       </c>
       <c r="T54">
+        <v>14</v>
+      </c>
+      <c r="U54">
+        <v>14</v>
+      </c>
+      <c r="V54">
         <v>14</v>
       </c>
       <c r="W54">
@@ -3239,8 +3329,14 @@
       <c r="N55">
         <v>12</v>
       </c>
+      <c r="P55">
+        <v>12</v>
+      </c>
       <c r="Q55">
         <v>12</v>
+      </c>
+      <c r="R55">
+        <v>9</v>
       </c>
       <c r="S55">
         <v>11</v>
@@ -3248,6 +3344,12 @@
       <c r="T55">
         <v>11</v>
       </c>
+      <c r="U55">
+        <v>12</v>
+      </c>
+      <c r="V55">
+        <v>12</v>
+      </c>
       <c r="W55">
         <v>12</v>
       </c>
@@ -3289,14 +3391,26 @@
       <c r="N56">
         <v>10</v>
       </c>
+      <c r="P56">
+        <v>9</v>
+      </c>
       <c r="Q56">
         <v>7</v>
       </c>
+      <c r="R56">
+        <v>6</v>
+      </c>
       <c r="S56">
         <v>10</v>
       </c>
       <c r="T56">
         <v>9</v>
+      </c>
+      <c r="U56">
+        <v>9</v>
+      </c>
+      <c r="V56">
+        <v>10</v>
       </c>
       <c r="W56">
         <v>10</v>
@@ -3339,15 +3453,27 @@
       <c r="N57">
         <v>12</v>
       </c>
+      <c r="P57">
+        <v>12</v>
+      </c>
       <c r="Q57">
         <v>11</v>
       </c>
+      <c r="R57">
+        <v>10</v>
+      </c>
       <c r="S57">
         <v>12</v>
       </c>
       <c r="T57">
         <v>11</v>
       </c>
+      <c r="U57">
+        <v>12</v>
+      </c>
+      <c r="V57">
+        <v>12</v>
+      </c>
       <c r="W57">
         <v>12</v>
       </c>
@@ -3389,13 +3515,25 @@
       <c r="N58">
         <v>8</v>
       </c>
+      <c r="P58">
+        <v>8</v>
+      </c>
       <c r="Q58">
         <v>6</v>
       </c>
+      <c r="R58">
+        <v>8</v>
+      </c>
       <c r="S58">
         <v>8</v>
       </c>
       <c r="T58">
+        <v>8</v>
+      </c>
+      <c r="U58">
+        <v>8</v>
+      </c>
+      <c r="V58">
         <v>8</v>
       </c>
       <c r="W58">
@@ -3455,7 +3593,7 @@
       </c>
       <c r="P59">
         <f t="shared" si="36"/>
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="Q59">
         <f t="shared" ref="Q59" si="37">SUM(Q49:Q58)</f>
@@ -3463,7 +3601,7 @@
       </c>
       <c r="R59">
         <f t="shared" ref="R59" si="38">SUM(R49:R58)</f>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="S59">
         <f t="shared" ref="S59" si="39">SUM(S49:S58)</f>
@@ -3475,11 +3613,11 @@
       </c>
       <c r="U59">
         <f t="shared" ref="U59" si="41">SUM(U49:U58)</f>
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="V59">
         <f t="shared" ref="V59" si="42">SUM(V49:V58)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W59">
         <f t="shared" ref="W59" si="43">SUM(W49:W58)</f>
